--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_19-04-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_19-04-2026.xlsx
@@ -1232,7 +1232,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>£51.7</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>£57.31</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>£49.55</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>£41.23</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>£74.18</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>£81.55</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>£86.21</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>£89.87</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>£59.2</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>£70.18</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
